--- a/Gerbers/PickAndPlace.xlsx
+++ b/Gerbers/PickAndPlace.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB1_2026_07_01" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB1_2026_07_03" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="83">
   <si>
     <t>Designator</t>
   </si>
@@ -97,10 +97,10 @@
     <t>29.845mm</t>
   </si>
   <si>
-    <t>-22.86mm</t>
-  </si>
-  <si>
-    <t>-23.613mm</t>
+    <t>-9.525mm</t>
+  </si>
+  <si>
+    <t>-8.772mm</t>
   </si>
   <si>
     <t>22kΩ</t>
@@ -118,6 +118,12 @@
     <t>34.925mm</t>
   </si>
   <si>
+    <t>-9.398mm</t>
+  </si>
+  <si>
+    <t>-8.645mm</t>
+  </si>
+  <si>
     <t>R4</t>
   </si>
   <si>
@@ -127,13 +133,13 @@
     <t>R5</t>
   </si>
   <si>
-    <t>49.022mm</t>
-  </si>
-  <si>
-    <t>-24.384mm</t>
-  </si>
-  <si>
-    <t>48.269mm</t>
+    <t>48.895mm</t>
+  </si>
+  <si>
+    <t>-8.763mm</t>
+  </si>
+  <si>
+    <t>48.142mm</t>
   </si>
   <si>
     <t>R6</t>
@@ -142,10 +148,10 @@
     <t>22.225mm</t>
   </si>
   <si>
-    <t>-9.779mm</t>
-  </si>
-  <si>
-    <t>-9.026mm</t>
+    <t>-23.368mm</t>
+  </si>
+  <si>
+    <t>-22.615mm</t>
   </si>
   <si>
     <t>P1</t>
@@ -160,24 +166,24 @@
     <t>28.575mm</t>
   </si>
   <si>
+    <t>-6.223mm</t>
+  </si>
+  <si>
+    <t>52.705mm</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
     <t>-26.543mm</t>
   </si>
   <si>
-    <t>52.705mm</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>-6.223mm</t>
-  </si>
-  <si>
     <t>XSMB</t>
   </si>
   <si>
@@ -190,13 +196,13 @@
     <t>51.734mm</t>
   </si>
   <si>
-    <t>-12.218mm</t>
+    <t>-13.996mm</t>
   </si>
   <si>
     <t>49.796mm</t>
   </si>
   <si>
-    <t>-10.218mm</t>
+    <t>-11.996mm</t>
   </si>
   <si>
     <t>D0</t>
@@ -211,7 +217,7 @@
     <t>41.703mm</t>
   </si>
   <si>
-    <t>-19.22mm</t>
+    <t>-12.743mm</t>
   </si>
   <si>
     <t>1.6EN</t>
@@ -226,13 +232,13 @@
     <t>52.623mm</t>
   </si>
   <si>
-    <t>-20.092mm</t>
+    <t>-21.743mm</t>
   </si>
   <si>
     <t>51.145mm</t>
   </si>
   <si>
-    <t>-19.092mm</t>
+    <t>-20.743mm</t>
   </si>
   <si>
     <t>D1</t>
@@ -765,7 +771,7 @@
         <v>22</v>
       </c>
       <c r="L3">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M3" t="s">
         <v>23</v>
@@ -812,7 +818,7 @@
         <v>22</v>
       </c>
       <c r="L4">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M4" t="s">
         <v>23</v>
@@ -838,19 +844,19 @@
         <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
         <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H5" t="s">
         <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="J5">
         <v>2</v>
@@ -859,7 +865,7 @@
         <v>22</v>
       </c>
       <c r="L5">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M5" t="s">
         <v>23</v>
@@ -873,7 +879,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -882,19 +888,19 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
         <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I6" t="s">
         <v>29</v>
@@ -906,7 +912,7 @@
         <v>22</v>
       </c>
       <c r="L6">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M6" t="s">
         <v>23</v>
@@ -920,7 +926,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -929,22 +935,22 @@
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J7">
         <v>2</v>
@@ -967,7 +973,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
@@ -976,22 +982,22 @@
         <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J8">
         <v>2</v>
@@ -1014,125 +1020,125 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J9">
         <v>20</v>
       </c>
       <c r="K9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L9">
         <v>180</v>
       </c>
       <c r="M9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J10">
         <v>20</v>
       </c>
       <c r="K10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L10">
         <v>180</v>
       </c>
       <c r="M10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J11">
         <v>7</v>
@@ -1147,39 +1153,39 @@
         <v>23</v>
       </c>
       <c r="N11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1194,39 +1200,39 @@
         <v>23</v>
       </c>
       <c r="N12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J13">
         <v>7</v>
@@ -1241,39 +1247,39 @@
         <v>23</v>
       </c>
       <c r="N13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -1288,10 +1294,10 @@
         <v>23</v>
       </c>
       <c r="N14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/Gerbers/PickAndPlace.xlsx
+++ b/Gerbers/PickAndPlace.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB1_2026_07_03" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB1_2026_07_21" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="87">
   <si>
     <t>Designator</t>
   </si>
@@ -85,10 +85,118 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>2.54-1*20P母</t>
+  </si>
+  <si>
+    <t>HDR-TH_20P-P2.54-V-F</t>
+  </si>
+  <si>
+    <t>28.575mm</t>
+  </si>
+  <si>
+    <t>-6.223mm</t>
+  </si>
+  <si>
+    <t>52.705mm</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>-26.543mm</t>
+  </si>
+  <si>
+    <t>XSMB</t>
+  </si>
+  <si>
+    <t>XDWF-0910-05P</t>
+  </si>
+  <si>
+    <t>CONN-SMD_XDWF-0910-05P</t>
+  </si>
+  <si>
+    <t>51.734mm</t>
+  </si>
+  <si>
+    <t>-13.996mm</t>
+  </si>
+  <si>
+    <t>49.796mm</t>
+  </si>
+  <si>
+    <t>-11.996mm</t>
+  </si>
+  <si>
+    <t>D0</t>
+  </si>
+  <si>
+    <t>Test-Point</t>
+  </si>
+  <si>
+    <t>Test-Point-0.5mm</t>
+  </si>
+  <si>
+    <t>41.703mm</t>
+  </si>
+  <si>
+    <t>-12.743mm</t>
+  </si>
+  <si>
+    <t>1.6EN</t>
+  </si>
+  <si>
+    <t>SK-3293S</t>
+  </si>
+  <si>
+    <t>SW-SMD_SK-3293S</t>
+  </si>
+  <si>
+    <t>52.623mm</t>
+  </si>
+  <si>
+    <t>-21.743mm</t>
+  </si>
+  <si>
+    <t>51.145mm</t>
+  </si>
+  <si>
+    <t>-20.743mm</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>1N4148WS_C2128</t>
+  </si>
+  <si>
+    <t>SOD-323_L1.8-W1.3-LS2.5-RD</t>
+  </si>
+  <si>
+    <t>47.035mm</t>
+  </si>
+  <si>
+    <t>-17.425mm</t>
+  </si>
+  <si>
+    <t>-18.598mm</t>
+  </si>
+  <si>
+    <t>1N4148WS</t>
+  </si>
+  <si>
     <t>R1</t>
   </si>
   <si>
-    <t>0603WAF2202T5E</t>
+    <t>RC0603FR-0722RL</t>
   </si>
   <si>
     <t>R0603</t>
@@ -103,163 +211,67 @@
     <t>-8.772mm</t>
   </si>
   <si>
-    <t>22kΩ</t>
+    <t>22Ω</t>
   </si>
   <si>
     <t>R2</t>
   </si>
   <si>
-    <t>27.234mm</t>
+    <t>27.293mm</t>
+  </si>
+  <si>
+    <t>-9.488mm</t>
+  </si>
+  <si>
+    <t>-8.735mm</t>
   </si>
   <si>
     <t>R3</t>
   </si>
   <si>
-    <t>34.925mm</t>
-  </si>
-  <si>
-    <t>-9.398mm</t>
-  </si>
-  <si>
-    <t>-8.645mm</t>
+    <t>34.913mm</t>
+  </si>
+  <si>
+    <t>-9.43mm</t>
+  </si>
+  <si>
+    <t>-8.677mm</t>
   </si>
   <si>
     <t>R4</t>
   </si>
   <si>
-    <t>32.433mm</t>
+    <t>32.373mm</t>
+  </si>
+  <si>
+    <t>-9.499mm</t>
+  </si>
+  <si>
+    <t>-8.745mm</t>
   </si>
   <si>
     <t>R5</t>
   </si>
   <si>
-    <t>48.895mm</t>
+    <t>49.022mm</t>
   </si>
   <si>
     <t>-8.763mm</t>
   </si>
   <si>
-    <t>48.142mm</t>
+    <t>49.775mm</t>
   </si>
   <si>
     <t>R6</t>
   </si>
   <si>
-    <t>22.225mm</t>
-  </si>
-  <si>
-    <t>-23.368mm</t>
-  </si>
-  <si>
-    <t>-22.615mm</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>2.54-1*20P母</t>
-  </si>
-  <si>
-    <t>HDR-TH_20P-P2.54-V-F</t>
-  </si>
-  <si>
-    <t>28.575mm</t>
-  </si>
-  <si>
-    <t>-6.223mm</t>
-  </si>
-  <si>
-    <t>52.705mm</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>-26.543mm</t>
-  </si>
-  <si>
-    <t>XSMB</t>
-  </si>
-  <si>
-    <t>XDWF-0910-05P</t>
-  </si>
-  <si>
-    <t>CONN-SMD_XDWF-0910-05P</t>
-  </si>
-  <si>
-    <t>51.734mm</t>
-  </si>
-  <si>
-    <t>-13.996mm</t>
-  </si>
-  <si>
-    <t>49.796mm</t>
-  </si>
-  <si>
-    <t>-11.996mm</t>
-  </si>
-  <si>
-    <t>D0</t>
-  </si>
-  <si>
-    <t>Test-Point</t>
-  </si>
-  <si>
-    <t>Test-Point-0.5mm</t>
-  </si>
-  <si>
-    <t>41.703mm</t>
-  </si>
-  <si>
-    <t>-12.743mm</t>
-  </si>
-  <si>
-    <t>1.6EN</t>
-  </si>
-  <si>
-    <t>SK-3293S</t>
-  </si>
-  <si>
-    <t>SW-SMD_SK-3293S</t>
-  </si>
-  <si>
-    <t>52.623mm</t>
-  </si>
-  <si>
-    <t>-21.743mm</t>
-  </si>
-  <si>
-    <t>51.145mm</t>
-  </si>
-  <si>
-    <t>-20.743mm</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>1N4148WS_C2128</t>
-  </si>
-  <si>
-    <t>SOD-323_L1.8-W1.3-LS2.5-RD</t>
-  </si>
-  <si>
-    <t>47.035mm</t>
-  </si>
-  <si>
-    <t>-17.425mm</t>
-  </si>
-  <si>
-    <t>-18.598mm</t>
-  </si>
-  <si>
-    <t>1N4148WS</t>
+    <t>22.204mm</t>
+  </si>
+  <si>
+    <t>-23.343mm</t>
+  </si>
+  <si>
+    <t>-22.59mm</t>
   </si>
 </sst>
 </file>
@@ -759,33 +771,33 @@
         <v>28</v>
       </c>
       <c r="H3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="L3">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="N3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
@@ -794,72 +806,72 @@
         <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K4" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="L4">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M4" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="N4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K5" t="s">
         <v>22</v>
@@ -871,133 +883,133 @@
         <v>23</v>
       </c>
       <c r="N5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="O5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="I6" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="s">
         <v>22</v>
       </c>
       <c r="L6">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M6" t="s">
         <v>23</v>
       </c>
       <c r="N6" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="O6" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="H7" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="I7" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="J7">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K7" t="s">
         <v>22</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M7" t="s">
         <v>23</v>
       </c>
       <c r="N7" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="O7" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="G8" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="J8">
         <v>2</v>
@@ -1006,142 +1018,142 @@
         <v>22</v>
       </c>
       <c r="L8">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="M8" t="s">
         <v>23</v>
       </c>
       <c r="N8" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="O8" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H9" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="I9" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="J9">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K9" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L9">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M9" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="N9" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="O9" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="G10" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H10" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="J10">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K10" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="L10">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M10" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="N10" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="O10" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="G11" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="I11" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="J11">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K11" t="s">
         <v>22</v>
@@ -1153,133 +1165,133 @@
         <v>23</v>
       </c>
       <c r="N11" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="O11" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="I12" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" t="s">
         <v>22</v>
       </c>
       <c r="L12">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M12" t="s">
         <v>23</v>
       </c>
       <c r="N12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E13" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F13" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I13" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="J13">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K13" t="s">
         <v>22</v>
       </c>
       <c r="L13">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="M13" t="s">
         <v>23</v>
       </c>
       <c r="N13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="O13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G14" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="H14" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J14">
         <v>2</v>
@@ -1288,16 +1300,16 @@
         <v>22</v>
       </c>
       <c r="L14">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="M14" t="s">
         <v>23</v>
       </c>
       <c r="N14" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="O14" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
